--- a/Results_experiment/exp_5/eval_cycle_XI.xlsx
+++ b/Results_experiment/exp_5/eval_cycle_XI.xlsx
@@ -447,13 +447,13 @@
         <v>534</v>
       </c>
       <c r="D2">
-        <v>-30.73691500991517</v>
+        <v>0.1627269446076666</v>
       </c>
       <c r="E2">
-        <v>37.62075591098188</v>
+        <v>6.110527750426343</v>
       </c>
       <c r="F2">
-        <v>30.28306056666519</v>
+        <v>4.125726687676563</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -467,13 +467,13 @@
         <v>521</v>
       </c>
       <c r="D3">
-        <v>-51.79292730684648</v>
+        <v>0.5581448033853822</v>
       </c>
       <c r="E3">
-        <v>43.7778547610073</v>
+        <v>4.005037508227693</v>
       </c>
       <c r="F3">
-        <v>27.78240634879945</v>
+        <v>2.573177704355195</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -487,13 +487,13 @@
         <v>429</v>
       </c>
       <c r="D4">
-        <v>-36.77891914063196</v>
+        <v>0.2541120723612214</v>
       </c>
       <c r="E4">
-        <v>47.84006684078911</v>
+        <v>6.722081946886363</v>
       </c>
       <c r="F4">
-        <v>41.58750789857411</v>
+        <v>4.167796078400734</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -507,13 +507,13 @@
         <v>374</v>
       </c>
       <c r="D5">
-        <v>-37.11984377222968</v>
+        <v>0.4386516877585249</v>
       </c>
       <c r="E5">
-        <v>28.44434186105848</v>
+        <v>3.451727830516917</v>
       </c>
       <c r="F5">
-        <v>17.43921720794337</v>
+        <v>2.4448149458052</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -527,13 +527,13 @@
         <v>251</v>
       </c>
       <c r="D6">
-        <v>-20.43600916569076</v>
+        <v>0.2796751857279072</v>
       </c>
       <c r="E6">
-        <v>21.9779297830351</v>
+        <v>4.028830557696127</v>
       </c>
       <c r="F6">
-        <v>14.58309490919351</v>
+        <v>2.700166042404346</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -547,13 +547,13 @@
         <v>237</v>
       </c>
       <c r="D7">
-        <v>-80.84229842650512</v>
+        <v>-0.7355414250129755</v>
       </c>
       <c r="E7">
-        <v>44.65953817068825</v>
+        <v>6.503435106018607</v>
       </c>
       <c r="F7">
-        <v>28.83106865501228</v>
+        <v>4.94218474340464</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -567,13 +567,13 @@
         <v>223</v>
       </c>
       <c r="D8">
-        <v>-19.72189360576566</v>
+        <v>0.419666696915787</v>
       </c>
       <c r="E8">
-        <v>17.70788211361112</v>
+        <v>2.963402542852458</v>
       </c>
       <c r="F8">
-        <v>12.59757369653125</v>
+        <v>2.233025952605656</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -587,13 +587,13 @@
         <v>84</v>
       </c>
       <c r="D9">
-        <v>-57.99204871976244</v>
+        <v>0.3242560273831553</v>
       </c>
       <c r="E9">
-        <v>74.64103627885135</v>
+        <v>7.988624559768868</v>
       </c>
       <c r="F9">
-        <v>54.42581898009493</v>
+        <v>5.024982005002952</v>
       </c>
     </row>
   </sheetData>
